--- a/GUA/IPPU/A1_Outputs/A-O_Demand_COMPLETED.xlsx
+++ b/GUA/IPPU/A1_Outputs/A-O_Demand_COMPLETED.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="39">
   <si>
     <t>Demand/Share</t>
   </si>
@@ -43,16 +43,94 @@
     <t>Demand</t>
   </si>
   <si>
-    <t>E5_CEM_PRODCEM_PROD</t>
-  </si>
-  <si>
-    <t>Demand Cement production Cement production</t>
+    <t>E5INDCEM_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPUGLASS_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>E5IPPUIRON_STEEL</t>
+  </si>
+  <si>
+    <t>E5IPPUPROD_FERRO</t>
+  </si>
+  <si>
+    <t>E5IPPULUBRI_OILS</t>
+  </si>
+  <si>
+    <t>E5IPPUPARAFFIN</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC143a</t>
+  </si>
+  <si>
+    <t>Demand Industrial Cement production</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Lime production calcitic</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Lime production dolomitic</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Glass production</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Carbonate ceramics</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Carbonate soda ash</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Iron and Steel production</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Ferroalloy production</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Use of Lubricants Oils</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Use of Paraffin Wax</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC32</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC125</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC134a</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC143a</t>
   </si>
   <si>
     <t>not needed</t>
   </si>
   <si>
-    <t>Otro</t>
+    <t>User defined</t>
   </si>
 </sst>
 </file>
@@ -410,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:AO15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:41">
@@ -546,37 +624,37 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>2.754</v>
+        <v>2.7546</v>
       </c>
       <c r="J2">
-        <v>2.867</v>
+        <v>3.0039</v>
       </c>
       <c r="K2">
-        <v>2.92</v>
+        <v>3.525</v>
       </c>
       <c r="L2">
-        <v>3.6211</v>
+        <v>4.2775</v>
       </c>
       <c r="M2">
-        <v>3.8986</v>
+        <v>4.6204</v>
       </c>
       <c r="N2">
         <v>5.708</v>
@@ -661,263 +739,1634 @@
       </c>
       <c r="AO2">
         <v>33.7216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0.2436</v>
+      </c>
+      <c r="J3">
+        <v>0.3239</v>
+      </c>
+      <c r="K3">
+        <v>0.4235</v>
+      </c>
+      <c r="L3">
+        <v>0.4008</v>
+      </c>
+      <c r="M3">
+        <v>0.4703</v>
+      </c>
+      <c r="N3">
+        <v>0.4882</v>
+      </c>
+      <c r="O3">
+        <v>0.5068</v>
+      </c>
+      <c r="P3">
+        <v>0.526</v>
+      </c>
+      <c r="Q3">
+        <v>0.546</v>
+      </c>
+      <c r="R3">
+        <v>0.5667</v>
+      </c>
+      <c r="S3">
+        <v>0.5883</v>
+      </c>
+      <c r="T3">
+        <v>0.6106</v>
+      </c>
+      <c r="U3">
+        <v>0.6338</v>
+      </c>
+      <c r="V3">
+        <v>0.6579</v>
+      </c>
+      <c r="W3">
+        <v>0.6829</v>
+      </c>
+      <c r="X3">
+        <v>0.7089</v>
+      </c>
+      <c r="Y3">
+        <v>0.7358</v>
+      </c>
+      <c r="Z3">
+        <v>0.7638</v>
+      </c>
+      <c r="AA3">
+        <v>0.7927999999999999</v>
+      </c>
+      <c r="AB3">
+        <v>0.8229</v>
+      </c>
+      <c r="AC3">
+        <v>0.8542</v>
+      </c>
+      <c r="AD3">
+        <v>0.8867</v>
+      </c>
+      <c r="AE3">
+        <v>0.9204</v>
+      </c>
+      <c r="AF3">
+        <v>0.9553</v>
+      </c>
+      <c r="AG3">
+        <v>0.9916</v>
+      </c>
+      <c r="AH3">
+        <v>1.0293</v>
+      </c>
+      <c r="AI3">
+        <v>1.0684</v>
+      </c>
+      <c r="AJ3">
+        <v>1.109</v>
+      </c>
+      <c r="AK3">
+        <v>1.1512</v>
+      </c>
+      <c r="AL3">
+        <v>1.1949</v>
+      </c>
+      <c r="AM3">
+        <v>1.2403</v>
+      </c>
+      <c r="AN3">
+        <v>1.2875</v>
+      </c>
+      <c r="AO3">
+        <v>1.3364</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0.003</v>
+      </c>
+      <c r="J4">
+        <v>0.0188</v>
+      </c>
+      <c r="K4">
+        <v>0.1</v>
+      </c>
+      <c r="L4">
+        <v>0.1081</v>
+      </c>
+      <c r="M4">
+        <v>0.1169</v>
+      </c>
+      <c r="N4">
+        <v>0.1213</v>
+      </c>
+      <c r="O4">
+        <v>0.1259</v>
+      </c>
+      <c r="P4">
+        <v>0.1307</v>
+      </c>
+      <c r="Q4">
+        <v>0.1356</v>
+      </c>
+      <c r="R4">
+        <v>0.1408</v>
+      </c>
+      <c r="S4">
+        <v>0.1462</v>
+      </c>
+      <c r="T4">
+        <v>0.1517</v>
+      </c>
+      <c r="U4">
+        <v>0.1575</v>
+      </c>
+      <c r="V4">
+        <v>0.1635</v>
+      </c>
+      <c r="W4">
+        <v>0.1697</v>
+      </c>
+      <c r="X4">
+        <v>0.1761</v>
+      </c>
+      <c r="Y4">
+        <v>0.1828</v>
+      </c>
+      <c r="Z4">
+        <v>0.1898</v>
+      </c>
+      <c r="AA4">
+        <v>0.197</v>
+      </c>
+      <c r="AB4">
+        <v>0.2045</v>
+      </c>
+      <c r="AC4">
+        <v>0.2122</v>
+      </c>
+      <c r="AD4">
+        <v>0.2203</v>
+      </c>
+      <c r="AE4">
+        <v>0.2287</v>
+      </c>
+      <c r="AF4">
+        <v>0.2373</v>
+      </c>
+      <c r="AG4">
+        <v>0.2464</v>
+      </c>
+      <c r="AH4">
+        <v>0.2557</v>
+      </c>
+      <c r="AI4">
+        <v>0.2654</v>
+      </c>
+      <c r="AJ4">
+        <v>0.2755</v>
+      </c>
+      <c r="AK4">
+        <v>0.286</v>
+      </c>
+      <c r="AL4">
+        <v>0.2969</v>
+      </c>
+      <c r="AM4">
+        <v>0.3081</v>
+      </c>
+      <c r="AN4">
+        <v>0.3199</v>
+      </c>
+      <c r="AO4">
+        <v>0.332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0.1146</v>
+      </c>
+      <c r="J5">
+        <v>0.1375</v>
+      </c>
+      <c r="K5">
+        <v>0.1796</v>
+      </c>
+      <c r="L5">
+        <v>0.1979</v>
+      </c>
+      <c r="M5">
+        <v>0.1714</v>
+      </c>
+      <c r="N5">
+        <v>0.1779</v>
+      </c>
+      <c r="O5">
+        <v>0.1846</v>
+      </c>
+      <c r="P5">
+        <v>0.1917</v>
+      </c>
+      <c r="Q5">
+        <v>0.1989</v>
+      </c>
+      <c r="R5">
+        <v>0.2065</v>
+      </c>
+      <c r="S5">
+        <v>0.2143</v>
+      </c>
+      <c r="T5">
+        <v>0.2225</v>
+      </c>
+      <c r="U5">
+        <v>0.2309</v>
+      </c>
+      <c r="V5">
+        <v>0.2397</v>
+      </c>
+      <c r="W5">
+        <v>0.2488</v>
+      </c>
+      <c r="X5">
+        <v>0.2583</v>
+      </c>
+      <c r="Y5">
+        <v>0.2681</v>
+      </c>
+      <c r="Z5">
+        <v>0.2783</v>
+      </c>
+      <c r="AA5">
+        <v>0.2889</v>
+      </c>
+      <c r="AB5">
+        <v>0.2998</v>
+      </c>
+      <c r="AC5">
+        <v>0.3112</v>
+      </c>
+      <c r="AD5">
+        <v>0.3231</v>
+      </c>
+      <c r="AE5">
+        <v>0.3353</v>
+      </c>
+      <c r="AF5">
+        <v>0.3481</v>
+      </c>
+      <c r="AG5">
+        <v>0.3613</v>
+      </c>
+      <c r="AH5">
+        <v>0.375</v>
+      </c>
+      <c r="AI5">
+        <v>0.3893</v>
+      </c>
+      <c r="AJ5">
+        <v>0.4041</v>
+      </c>
+      <c r="AK5">
+        <v>0.4194</v>
+      </c>
+      <c r="AL5">
+        <v>0.4354</v>
+      </c>
+      <c r="AM5">
+        <v>0.4519</v>
+      </c>
+      <c r="AN5">
+        <v>0.4691</v>
+      </c>
+      <c r="AO5">
+        <v>0.4869</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0.0593</v>
+      </c>
+      <c r="J6">
+        <v>0.0066</v>
+      </c>
+      <c r="K6">
+        <v>0.0205</v>
+      </c>
+      <c r="L6">
+        <v>0.0248</v>
+      </c>
+      <c r="M6">
+        <v>0.0301</v>
+      </c>
+      <c r="N6">
+        <v>0.0312</v>
+      </c>
+      <c r="O6">
+        <v>0.0324</v>
+      </c>
+      <c r="P6">
+        <v>0.0336</v>
+      </c>
+      <c r="Q6">
+        <v>0.0349</v>
+      </c>
+      <c r="R6">
+        <v>0.0362</v>
+      </c>
+      <c r="S6">
+        <v>0.0376</v>
+      </c>
+      <c r="T6">
+        <v>0.039</v>
+      </c>
+      <c r="U6">
+        <v>0.0405</v>
+      </c>
+      <c r="V6">
+        <v>0.0421</v>
+      </c>
+      <c r="W6">
+        <v>0.0437</v>
+      </c>
+      <c r="X6">
+        <v>0.0453</v>
+      </c>
+      <c r="Y6">
+        <v>0.047</v>
+      </c>
+      <c r="Z6">
+        <v>0.0488</v>
+      </c>
+      <c r="AA6">
+        <v>0.0507</v>
+      </c>
+      <c r="AB6">
+        <v>0.0526</v>
+      </c>
+      <c r="AC6">
+        <v>0.0546</v>
+      </c>
+      <c r="AD6">
+        <v>0.0567</v>
+      </c>
+      <c r="AE6">
+        <v>0.0588</v>
+      </c>
+      <c r="AF6">
+        <v>0.0611</v>
+      </c>
+      <c r="AG6">
+        <v>0.0634</v>
+      </c>
+      <c r="AH6">
+        <v>0.0658</v>
+      </c>
+      <c r="AI6">
+        <v>0.0683</v>
+      </c>
+      <c r="AJ6">
+        <v>0.0709</v>
+      </c>
+      <c r="AK6">
+        <v>0.0736</v>
+      </c>
+      <c r="AL6">
+        <v>0.0764</v>
+      </c>
+      <c r="AM6">
+        <v>0.0793</v>
+      </c>
+      <c r="AN6">
+        <v>0.0823</v>
+      </c>
+      <c r="AO6">
+        <v>0.0854</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0.0216</v>
+      </c>
+      <c r="J7">
+        <v>0.0308</v>
+      </c>
+      <c r="K7">
+        <v>0.0288</v>
+      </c>
+      <c r="L7">
+        <v>0.0356</v>
+      </c>
+      <c r="M7">
+        <v>0.0367</v>
+      </c>
+      <c r="N7">
+        <v>0.0381</v>
+      </c>
+      <c r="O7">
+        <v>0.0396</v>
+      </c>
+      <c r="P7">
+        <v>0.0411</v>
+      </c>
+      <c r="Q7">
+        <v>0.0426</v>
+      </c>
+      <c r="R7">
+        <v>0.0443</v>
+      </c>
+      <c r="S7">
+        <v>0.0459</v>
+      </c>
+      <c r="T7">
+        <v>0.0477</v>
+      </c>
+      <c r="U7">
+        <v>0.0495</v>
+      </c>
+      <c r="V7">
+        <v>0.0514</v>
+      </c>
+      <c r="W7">
+        <v>0.0533</v>
+      </c>
+      <c r="X7">
+        <v>0.0554</v>
+      </c>
+      <c r="Y7">
+        <v>0.0575</v>
+      </c>
+      <c r="Z7">
+        <v>0.0596</v>
+      </c>
+      <c r="AA7">
+        <v>0.0619</v>
+      </c>
+      <c r="AB7">
+        <v>0.0643</v>
+      </c>
+      <c r="AC7">
+        <v>0.0667</v>
+      </c>
+      <c r="AD7">
+        <v>0.0692</v>
+      </c>
+      <c r="AE7">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="AF7">
+        <v>0.0746</v>
+      </c>
+      <c r="AG7">
+        <v>0.0774</v>
+      </c>
+      <c r="AH7">
+        <v>0.0804</v>
+      </c>
+      <c r="AI7">
+        <v>0.0834</v>
+      </c>
+      <c r="AJ7">
+        <v>0.0866</v>
+      </c>
+      <c r="AK7">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="AL7">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="AM7">
+        <v>0.0968</v>
+      </c>
+      <c r="AN7">
+        <v>0.1005</v>
+      </c>
+      <c r="AO7">
+        <v>0.1043</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.2812</v>
+      </c>
+      <c r="J8">
+        <v>0.294</v>
+      </c>
+      <c r="K8">
+        <v>0.3069</v>
+      </c>
+      <c r="L8">
+        <v>0.2711</v>
+      </c>
+      <c r="M8">
+        <v>0.1335</v>
+      </c>
+      <c r="N8">
+        <v>0.1386</v>
+      </c>
+      <c r="O8">
+        <v>0.1438</v>
+      </c>
+      <c r="P8">
+        <v>0.1493</v>
+      </c>
+      <c r="Q8">
+        <v>0.155</v>
+      </c>
+      <c r="R8">
+        <v>0.1609</v>
+      </c>
+      <c r="S8">
+        <v>0.167</v>
+      </c>
+      <c r="T8">
+        <v>0.1733</v>
+      </c>
+      <c r="U8">
+        <v>0.1799</v>
+      </c>
+      <c r="V8">
+        <v>0.1867</v>
+      </c>
+      <c r="W8">
+        <v>0.1938</v>
+      </c>
+      <c r="X8">
+        <v>0.2012</v>
+      </c>
+      <c r="Y8">
+        <v>0.2089</v>
+      </c>
+      <c r="Z8">
+        <v>0.2168</v>
+      </c>
+      <c r="AA8">
+        <v>0.225</v>
+      </c>
+      <c r="AB8">
+        <v>0.2336</v>
+      </c>
+      <c r="AC8">
+        <v>0.2425</v>
+      </c>
+      <c r="AD8">
+        <v>0.2517</v>
+      </c>
+      <c r="AE8">
+        <v>0.2612</v>
+      </c>
+      <c r="AF8">
+        <v>0.2712</v>
+      </c>
+      <c r="AG8">
+        <v>0.2815</v>
+      </c>
+      <c r="AH8">
+        <v>0.2922</v>
+      </c>
+      <c r="AI8">
+        <v>0.3033</v>
+      </c>
+      <c r="AJ8">
+        <v>0.3148</v>
+      </c>
+      <c r="AK8">
+        <v>0.3268</v>
+      </c>
+      <c r="AL8">
+        <v>0.3392</v>
+      </c>
+      <c r="AM8">
+        <v>0.3521</v>
+      </c>
+      <c r="AN8">
+        <v>0.3654</v>
+      </c>
+      <c r="AO8">
+        <v>0.3793</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0.3735</v>
+      </c>
+      <c r="J9">
+        <v>0.4729</v>
+      </c>
+      <c r="K9">
+        <v>0.5724</v>
+      </c>
+      <c r="L9">
+        <v>0.0605</v>
+      </c>
+      <c r="M9">
+        <v>0.0279</v>
+      </c>
+      <c r="N9">
+        <v>0.029</v>
+      </c>
+      <c r="O9">
+        <v>0.0301</v>
+      </c>
+      <c r="P9">
+        <v>0.0312</v>
+      </c>
+      <c r="Q9">
+        <v>0.0324</v>
+      </c>
+      <c r="R9">
+        <v>0.0336</v>
+      </c>
+      <c r="S9">
+        <v>0.0349</v>
+      </c>
+      <c r="T9">
+        <v>0.0363</v>
+      </c>
+      <c r="U9">
+        <v>0.0376</v>
+      </c>
+      <c r="V9">
+        <v>0.0391</v>
+      </c>
+      <c r="W9">
+        <v>0.0405</v>
+      </c>
+      <c r="X9">
+        <v>0.0421</v>
+      </c>
+      <c r="Y9">
+        <v>0.0437</v>
+      </c>
+      <c r="Z9">
+        <v>0.0453</v>
+      </c>
+      <c r="AA9">
+        <v>0.0471</v>
+      </c>
+      <c r="AB9">
+        <v>0.0489</v>
+      </c>
+      <c r="AC9">
+        <v>0.0507</v>
+      </c>
+      <c r="AD9">
+        <v>0.0526</v>
+      </c>
+      <c r="AE9">
+        <v>0.0546</v>
+      </c>
+      <c r="AF9">
+        <v>0.0567</v>
+      </c>
+      <c r="AG9">
+        <v>0.0589</v>
+      </c>
+      <c r="AH9">
+        <v>0.0611</v>
+      </c>
+      <c r="AI9">
+        <v>0.0634</v>
+      </c>
+      <c r="AJ9">
+        <v>0.0658</v>
+      </c>
+      <c r="AK9">
+        <v>0.0683</v>
+      </c>
+      <c r="AL9">
+        <v>0.0709</v>
+      </c>
+      <c r="AM9">
+        <v>0.0736</v>
+      </c>
+      <c r="AN9">
+        <v>0.0764</v>
+      </c>
+      <c r="AO9">
+        <v>0.0793</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0.0442</v>
+      </c>
+      <c r="J10">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="K10">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="L10">
+        <v>0.0598</v>
+      </c>
+      <c r="M10">
+        <v>0.0598</v>
+      </c>
+      <c r="N10">
+        <v>0.062</v>
+      </c>
+      <c r="O10">
+        <v>0.0644</v>
+      </c>
+      <c r="P10">
+        <v>0.0668</v>
+      </c>
+      <c r="Q10">
+        <v>0.0694</v>
+      </c>
+      <c r="R10">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="S10">
+        <v>0.0747</v>
+      </c>
+      <c r="T10">
+        <v>0.0776</v>
+      </c>
+      <c r="U10">
+        <v>0.0805</v>
+      </c>
+      <c r="V10">
+        <v>0.08359999999999999</v>
+      </c>
+      <c r="W10">
+        <v>0.0868</v>
+      </c>
+      <c r="X10">
+        <v>0.0901</v>
+      </c>
+      <c r="Y10">
+        <v>0.0935</v>
+      </c>
+      <c r="Z10">
+        <v>0.097</v>
+      </c>
+      <c r="AA10">
+        <v>0.1007</v>
+      </c>
+      <c r="AB10">
+        <v>0.1045</v>
+      </c>
+      <c r="AC10">
+        <v>0.1085</v>
+      </c>
+      <c r="AD10">
+        <v>0.1126</v>
+      </c>
+      <c r="AE10">
+        <v>0.1169</v>
+      </c>
+      <c r="AF10">
+        <v>0.1214</v>
+      </c>
+      <c r="AG10">
+        <v>0.126</v>
+      </c>
+      <c r="AH10">
+        <v>0.1308</v>
+      </c>
+      <c r="AI10">
+        <v>0.1357</v>
+      </c>
+      <c r="AJ10">
+        <v>0.1409</v>
+      </c>
+      <c r="AK10">
+        <v>0.1462</v>
+      </c>
+      <c r="AL10">
+        <v>0.1518</v>
+      </c>
+      <c r="AM10">
+        <v>0.1576</v>
+      </c>
+      <c r="AN10">
+        <v>0.1636</v>
+      </c>
+      <c r="AO10">
+        <v>0.1698</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0.0092</v>
+      </c>
+      <c r="J11">
+        <v>0.0019</v>
+      </c>
+      <c r="K11">
+        <v>0.0031</v>
+      </c>
+      <c r="L11">
+        <v>0.0165</v>
+      </c>
+      <c r="M11">
+        <v>0.0167</v>
+      </c>
+      <c r="N11">
+        <v>0.0173</v>
+      </c>
+      <c r="O11">
+        <v>0.018</v>
+      </c>
+      <c r="P11">
+        <v>0.0186</v>
+      </c>
+      <c r="Q11">
+        <v>0.0194</v>
+      </c>
+      <c r="R11">
+        <v>0.0201</v>
+      </c>
+      <c r="S11">
+        <v>0.0209</v>
+      </c>
+      <c r="T11">
+        <v>0.0216</v>
+      </c>
+      <c r="U11">
+        <v>0.0225</v>
+      </c>
+      <c r="V11">
+        <v>0.0233</v>
+      </c>
+      <c r="W11">
+        <v>0.0242</v>
+      </c>
+      <c r="X11">
+        <v>0.0251</v>
+      </c>
+      <c r="Y11">
+        <v>0.0261</v>
+      </c>
+      <c r="Z11">
+        <v>0.0271</v>
+      </c>
+      <c r="AA11">
+        <v>0.0281</v>
+      </c>
+      <c r="AB11">
+        <v>0.0292</v>
+      </c>
+      <c r="AC11">
+        <v>0.0303</v>
+      </c>
+      <c r="AD11">
+        <v>0.0314</v>
+      </c>
+      <c r="AE11">
+        <v>0.0326</v>
+      </c>
+      <c r="AF11">
+        <v>0.0339</v>
+      </c>
+      <c r="AG11">
+        <v>0.0351</v>
+      </c>
+      <c r="AH11">
+        <v>0.0365</v>
+      </c>
+      <c r="AI11">
+        <v>0.0379</v>
+      </c>
+      <c r="AJ11">
+        <v>0.0393</v>
+      </c>
+      <c r="AK11">
+        <v>0.0408</v>
+      </c>
+      <c r="AL11">
+        <v>0.0424</v>
+      </c>
+      <c r="AM11">
+        <v>0.044</v>
+      </c>
+      <c r="AN11">
+        <v>0.0456</v>
+      </c>
+      <c r="AO11">
+        <v>0.0474</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0.0165</v>
+      </c>
+      <c r="J12">
+        <v>0.0285</v>
+      </c>
+      <c r="K12">
+        <v>0.0349</v>
+      </c>
+      <c r="L12">
+        <v>0.0394</v>
+      </c>
+      <c r="M12">
+        <v>0.0519</v>
+      </c>
+      <c r="N12">
+        <v>0.0532</v>
+      </c>
+      <c r="O12">
+        <v>0.0545</v>
+      </c>
+      <c r="P12">
+        <v>0.0559</v>
+      </c>
+      <c r="Q12">
+        <v>0.0573</v>
+      </c>
+      <c r="R12">
+        <v>0.0587</v>
+      </c>
+      <c r="S12">
+        <v>0.0602</v>
+      </c>
+      <c r="T12">
+        <v>0.0617</v>
+      </c>
+      <c r="U12">
+        <v>0.0633</v>
+      </c>
+      <c r="V12">
+        <v>0.0648</v>
+      </c>
+      <c r="W12">
+        <v>0.0665</v>
+      </c>
+      <c r="X12">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="Y12">
+        <v>0.0698</v>
+      </c>
+      <c r="Z12">
+        <v>0.0716</v>
+      </c>
+      <c r="AA12">
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="AB12">
+        <v>0.0752</v>
+      </c>
+      <c r="AC12">
+        <v>0.0771</v>
+      </c>
+      <c r="AD12">
+        <v>0.079</v>
+      </c>
+      <c r="AE12">
+        <v>0.081</v>
+      </c>
+      <c r="AF12">
+        <v>0.083</v>
+      </c>
+      <c r="AG12">
+        <v>0.0851</v>
+      </c>
+      <c r="AH12">
+        <v>0.0872</v>
+      </c>
+      <c r="AI12">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="AJ12">
+        <v>0.0916</v>
+      </c>
+      <c r="AK12">
+        <v>0.0939</v>
+      </c>
+      <c r="AL12">
+        <v>0.0963</v>
+      </c>
+      <c r="AM12">
+        <v>0.0987</v>
+      </c>
+      <c r="AN12">
+        <v>0.1011</v>
+      </c>
+      <c r="AO12">
+        <v>0.1037</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0.0175</v>
+      </c>
+      <c r="J13">
+        <v>0.0238</v>
+      </c>
+      <c r="K13">
+        <v>0.0291</v>
+      </c>
+      <c r="L13">
+        <v>0.0321</v>
+      </c>
+      <c r="M13">
+        <v>0.0429</v>
+      </c>
+      <c r="N13">
+        <v>0.044</v>
+      </c>
+      <c r="O13">
+        <v>0.0451</v>
+      </c>
+      <c r="P13">
+        <v>0.0462</v>
+      </c>
+      <c r="Q13">
+        <v>0.0474</v>
+      </c>
+      <c r="R13">
+        <v>0.0486</v>
+      </c>
+      <c r="S13">
+        <v>0.0498</v>
+      </c>
+      <c r="T13">
+        <v>0.051</v>
+      </c>
+      <c r="U13">
+        <v>0.0523</v>
+      </c>
+      <c r="V13">
+        <v>0.0536</v>
+      </c>
+      <c r="W13">
+        <v>0.0549</v>
+      </c>
+      <c r="X13">
+        <v>0.0563</v>
+      </c>
+      <c r="Y13">
+        <v>0.0577</v>
+      </c>
+      <c r="Z13">
+        <v>0.0592</v>
+      </c>
+      <c r="AA13">
+        <v>0.0606</v>
+      </c>
+      <c r="AB13">
+        <v>0.0622</v>
+      </c>
+      <c r="AC13">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="AD13">
+        <v>0.0653</v>
+      </c>
+      <c r="AE13">
+        <v>0.0669</v>
+      </c>
+      <c r="AF13">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="AG13">
+        <v>0.0703</v>
+      </c>
+      <c r="AH13">
+        <v>0.0721</v>
+      </c>
+      <c r="AI13">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="AJ13">
+        <v>0.0757</v>
+      </c>
+      <c r="AK13">
+        <v>0.0776</v>
+      </c>
+      <c r="AL13">
+        <v>0.0796</v>
+      </c>
+      <c r="AM13">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="AN13">
+        <v>0.08359999999999999</v>
+      </c>
+      <c r="AO13">
+        <v>0.0857</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0.0209</v>
+      </c>
+      <c r="J14">
+        <v>0.0222</v>
+      </c>
+      <c r="K14">
+        <v>0.0649</v>
+      </c>
+      <c r="L14">
+        <v>0.1002</v>
+      </c>
+      <c r="M14">
+        <v>0.1397</v>
+      </c>
+      <c r="N14">
+        <v>0.1432</v>
+      </c>
+      <c r="O14">
+        <v>0.1468</v>
+      </c>
+      <c r="P14">
+        <v>0.1505</v>
+      </c>
+      <c r="Q14">
+        <v>0.1542</v>
+      </c>
+      <c r="R14">
+        <v>0.1581</v>
+      </c>
+      <c r="S14">
+        <v>0.162</v>
+      </c>
+      <c r="T14">
+        <v>0.1661</v>
+      </c>
+      <c r="U14">
+        <v>0.1702</v>
+      </c>
+      <c r="V14">
+        <v>0.1745</v>
+      </c>
+      <c r="W14">
+        <v>0.1789</v>
+      </c>
+      <c r="X14">
+        <v>0.1833</v>
+      </c>
+      <c r="Y14">
+        <v>0.1879</v>
+      </c>
+      <c r="Z14">
+        <v>0.1926</v>
+      </c>
+      <c r="AA14">
+        <v>0.1974</v>
+      </c>
+      <c r="AB14">
+        <v>0.2024</v>
+      </c>
+      <c r="AC14">
+        <v>0.2074</v>
+      </c>
+      <c r="AD14">
+        <v>0.2126</v>
+      </c>
+      <c r="AE14">
+        <v>0.2179</v>
+      </c>
+      <c r="AF14">
+        <v>0.2234</v>
+      </c>
+      <c r="AG14">
+        <v>0.2289</v>
+      </c>
+      <c r="AH14">
+        <v>0.2347</v>
+      </c>
+      <c r="AI14">
+        <v>0.2405</v>
+      </c>
+      <c r="AJ14">
+        <v>0.2465</v>
+      </c>
+      <c r="AK14">
+        <v>0.2527</v>
+      </c>
+      <c r="AL14">
+        <v>0.259</v>
+      </c>
+      <c r="AM14">
+        <v>0.2655</v>
+      </c>
+      <c r="AN14">
+        <v>0.2721</v>
+      </c>
+      <c r="AO14">
+        <v>0.2789</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.0139</v>
+      </c>
+      <c r="J15">
+        <v>0.0235</v>
+      </c>
+      <c r="K15">
+        <v>0.0279</v>
+      </c>
+      <c r="L15">
+        <v>0.0309</v>
+      </c>
+      <c r="M15">
+        <v>0.0363</v>
+      </c>
+      <c r="N15">
+        <v>0.0372</v>
+      </c>
+      <c r="O15">
+        <v>0.0382</v>
+      </c>
+      <c r="P15">
+        <v>0.0391</v>
+      </c>
+      <c r="Q15">
+        <v>0.0401</v>
+      </c>
+      <c r="R15">
+        <v>0.0411</v>
+      </c>
+      <c r="S15">
+        <v>0.0421</v>
+      </c>
+      <c r="T15">
+        <v>0.0432</v>
+      </c>
+      <c r="U15">
+        <v>0.0443</v>
+      </c>
+      <c r="V15">
+        <v>0.0454</v>
+      </c>
+      <c r="W15">
+        <v>0.0465</v>
+      </c>
+      <c r="X15">
+        <v>0.0477</v>
+      </c>
+      <c r="Y15">
+        <v>0.0489</v>
+      </c>
+      <c r="Z15">
+        <v>0.0501</v>
+      </c>
+      <c r="AA15">
+        <v>0.0513</v>
+      </c>
+      <c r="AB15">
+        <v>0.0526</v>
+      </c>
+      <c r="AC15">
+        <v>0.0539</v>
+      </c>
+      <c r="AD15">
+        <v>0.0553</v>
+      </c>
+      <c r="AE15">
+        <v>0.0567</v>
+      </c>
+      <c r="AF15">
+        <v>0.0581</v>
+      </c>
+      <c r="AG15">
+        <v>0.0595</v>
+      </c>
+      <c r="AH15">
+        <v>0.061</v>
+      </c>
+      <c r="AI15">
+        <v>0.0625</v>
+      </c>
+      <c r="AJ15">
+        <v>0.0641</v>
+      </c>
+      <c r="AK15">
+        <v>0.06569999999999999</v>
+      </c>
+      <c r="AL15">
+        <v>0.0673</v>
+      </c>
+      <c r="AM15">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="AN15">
+        <v>0.0708</v>
+      </c>
+      <c r="AO15">
+        <v>0.0725</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75cb9a07855af6ac97bd432464ca7c04">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1676634304aab9936f6a5a5f53c7423" ns2:_="" ns3:_="">
-    <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
-    <xsd:import namespace="081a93ea-d517-42a5-a2b7-457060aa7471"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="19" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="081a93ea-d517-42a5-a2b7-457060aa7471" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D7745AD-89BC-46CF-9350-9420DC15D567}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B776806-A067-4D1B-BE50-73CB48EA074F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{936C1220-82C4-42D1-9F50-2DD70810A96A}"/>
 </file>